--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>91.48</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=91.48</t>
+          <t>FRED=97.26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>424460</t>
+          <t>424069</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.7166</t>
+          <t>FRED=0.7209</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.7166</v>
+        <v>0.7209</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=14.32</t>
+          <t>FRED=17.84</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>14.32</v>
+        <v>17.84</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -771,7 +771,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -786,10 +786,10 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>3.54</v>
+        <v>3.71</v>
       </c>
       <c r="N9" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -822,10 +822,10 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>4.77</v>
+        <v>4.95</v>
       </c>
       <c r="P10" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>97.26000000000001</v>
+        <v>107.02</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=97.26</t>
+          <t>FRED=107.02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>424069</t>
+          <t>423429</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.7209</t>
+          <t>FRED=0.7174</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.7209</v>
+        <v>0.7174</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=17.84</t>
+          <t>FRED=15.44</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>17.84</v>
+        <v>15.44</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -822,10 +822,10 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>4.95</v>
+        <v>4.94</v>
       </c>
       <c r="P10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>107.02</v>
+        <v>96.41</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=107.02</t>
+          <t>FRED=96.41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>423429</t>
+          <t>426398</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.7174</t>
+          <t>FRED=0.7111</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.7174</v>
+        <v>0.7111</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=15.44</t>
+          <t>FRED=14.21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>15.44</v>
+        <v>14.21</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -822,10 +822,10 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>4.94</v>
+        <v>5.18</v>
       </c>
       <c r="P10" t="n">
-        <v>0.23</v>
+        <v>0.54</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -525,17 +525,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>331.9</v>
+        <v>333.2</v>
       </c>
       <c r="C2" t="n">
         <v>326.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>96.41</v>
+        <v>96.16</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=96.41</t>
+          <t>FRED=96.16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>426398</t>
+          <t>427320</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.7111</t>
+          <t>FRED=0.7033</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.7111</v>
+        <v>0.7033</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=14.21</t>
+          <t>FRED=16.39</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>14.21</v>
+        <v>16.39</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -822,10 +822,10 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>5.18</v>
+        <v>5.24</v>
       </c>
       <c r="P10" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.31</v>
+        <v>0.46</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -930,9 +930,11 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T13" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>96.16</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=96.16</t>
+          <t>FRED=96.24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>427320</t>
+          <t>424134</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.7033</t>
+          <t>FRED=0.6953</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.7033</v>
+        <v>0.6953</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=16.39</t>
+          <t>FRED=15.41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>16.39</v>
+        <v>15.41</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -822,10 +822,10 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="P10" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -932,9 +932,7 @@
       <c r="S13" t="n">
         <v>0.6</v>
       </c>
-      <c r="T13" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>96.23999999999999</v>
+        <v>101.91</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=96.24</t>
+          <t>FRED=101.91</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>424134</t>
+          <t>415577</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.6953</t>
+          <t>FRED=0.6979</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.6953</v>
+        <v>0.6979</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=15.41</t>
+          <t>FRED=16.46</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>15.41</v>
+        <v>16.46</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -771,7 +771,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -786,10 +786,10 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>3.71</v>
+        <v>4.02</v>
       </c>
       <c r="N9" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -822,10 +822,10 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="P10" t="n">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>

--- a/data/macro_signals.xlsx
+++ b/data/macro_signals.xlsx
@@ -605,16 +605,16 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>101.91</v>
+        <v>107.89</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FRED=101.91</t>
+          <t>FRED=107.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>415577</t>
+          <t>412517</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,12 +647,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRED=0.6979</t>
+          <t>FRED=0.6950</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.6979</v>
+        <v>0.695</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRED=16.46</t>
+          <t>FRED=19.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>16.46</v>
+        <v>19.03</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -822,11 +822,9 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.1</v>
-      </c>
+        <v>4.96</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -858,7 +856,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
